--- a/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE_bsdw157/stochastic_s3_r5_REINFORCE_with_CV.xlsx
+++ b/apps_nicolo/stochastic_RPA_3s_5r_MAK_REINFORCE_bsdw157/stochastic_s3_r5_REINFORCE_with_CV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.4765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="21" customWidth="1" style="3" min="1" max="1"/>
@@ -1549,95 +1549,183 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2025-12-23 09:48:40</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce-with-cv/1003327fde384b259e80c8c770012786</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>(6, 4, 2, 160)</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>1024</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>10240</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R12" t="n">
-        <v>100</v>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="R12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t>{'type': 'lognormal_1D'}</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W12" s="3" t="inlineStr">
         <is>
           <t>{'structure': 3.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>{'target_entropy_ratio_to_max': np.float64(0.30072507011480887), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:52:15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/stochastic-s3-r5-reinforce-with-cv/ba28f181df8e4fb589c6e7efc65d8b3e</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>600</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(6, 4, 2, 160)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30</v>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>{'structure': 3.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.30072507011480887), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z12"/>
+  <autoFilter ref="A1:Z13"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
